--- a/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:08:12+00:00</t>
+    <t>2026-04-14T15:34:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T15:34:16+00:00</t>
+    <t>2026-04-30T09:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T09:49:26+00:00</t>
+    <t>2026-05-12T12:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T12:57:02+00:00</t>
+    <t>2026-05-12T16:45:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
+++ b/AnalysePharma/ig/StructureDefinition-fr-analyse-pharmaceutique-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T16:45:43+00:00</t>
+    <t>2026-05-18T17:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
